--- a/Dados/tabPSANOS_RS_10.xlsx
+++ b/Dados/tabPSANOS_RS_10.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="11_A26B31483D9ECC1970ED903C59266AF99484E4FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E5D7AA4-4834-4F57-ACA5-D8F6C3920CF7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="N TOTAL PRINCIPAL" sheetId="1" r:id="rId1"/>
@@ -199,6 +199,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
